--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/COLORADO_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/COLORADO_2012.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C136">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C187">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C221">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C704">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C766">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C785">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C789">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1109">
@@ -22038,7 +22038,7 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1205">
